--- a/site/leagues/betclic/2026_2027/xlsx/shot_packs/shot_pack_UDO.xlsx
+++ b/site/leagues/betclic/2026_2027/xlsx/shot_packs/shot_pack_UDO.xlsx
@@ -654,16 +654,16 @@
         </is>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="T2" t="n">
         <v>2</v>
       </c>
       <c r="U2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="V2" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="W2" t="n">
         <v>10</v>

--- a/site/leagues/betclic/2026_2027/xlsx/shot_packs/shot_pack_UDO.xlsx
+++ b/site/leagues/betclic/2026_2027/xlsx/shot_packs/shot_pack_UDO.xlsx
@@ -21,14 +21,14 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'overview'!$A$1:$W$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'alerts'!$A$1:$B$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'players_volume'!$A$1:$S$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'players_eff'!$A$1:$S$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'players_3pt_volume'!$A$1:$N$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'players_3pt_pct'!$A$1:$A$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'players_volume'!$A$1:$S$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'players_eff'!$A$1:$S$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'players_3pt_volume'!$A$1:$N$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'players_3pt_pct'!$A$1:$N$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'team_zones'!$A$1:$I$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'preferred_areas'!$A$1:$P$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'player_zones_volume'!$A$1:$K$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'player_zones_pct'!$A$1:$A$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'preferred_areas'!$A$1:$P$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'player_zones_volume'!$A$1:$K$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'player_zones_pct'!$A$1:$K$6</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -590,83 +590,83 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>71</v>
+        <v>143</v>
       </c>
       <c r="D2" t="n">
-        <v>35</v>
+        <v>58</v>
       </c>
       <c r="E2" t="n">
-        <v>77</v>
+        <v>128</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>49.3%</t>
+          <t>40.6%</t>
         </is>
       </c>
       <c r="G2" t="n">
+        <v>86</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>53.5%</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>57</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>21.1%</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>39.9%</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="N2" t="n">
+        <v>45</v>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>48.9%</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="Q2" t="n">
         <v>43</v>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>65.1%</t>
-        </is>
-      </c>
-      <c r="I2" t="n">
-        <v>28</v>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>25.0%</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>39.4%</t>
-        </is>
-      </c>
-      <c r="L2" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="N2" t="n">
-        <v>26</v>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>65.4%</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="Q2" t="n">
-        <v>20</v>
-      </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>20.9%</t>
         </is>
       </c>
       <c r="S2" t="n">
+        <v>11</v>
+      </c>
+      <c r="T2" t="n">
+        <v>10</v>
+      </c>
+      <c r="U2" t="n">
+        <v>10</v>
+      </c>
+      <c r="V2" t="n">
+        <v>11</v>
+      </c>
+      <c r="W2" t="n">
         <v>12</v>
-      </c>
-      <c r="T2" t="n">
-        <v>2</v>
-      </c>
-      <c r="U2" t="n">
-        <v>5</v>
-      </c>
-      <c r="V2" t="n">
-        <v>12</v>
-      </c>
-      <c r="W2" t="n">
-        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -681,28 +681,306 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:K6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="28" customWidth="1" min="10" max="10"/>
+    <col width="25" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>player_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>player_name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>zone</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>attempts</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>made</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>points</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>fg_pct</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>pps</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>zone_share</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>player_zone_rank_by_volume</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>player_zone_rank_by_pct</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>sem dados</t>
-        </is>
+          <t>UDO_C._RODGER</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>C. Rodger</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>8</v>
+      </c>
+      <c r="E2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F2" t="n">
+        <v>8</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>UDO_P._NIXON</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>P. Nixon</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>11</v>
+      </c>
+      <c r="E3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F3" t="n">
+        <v>8</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>36.4%</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>39.3%</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>UDO_G._POWELL</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>G. Powell</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>10</v>
+      </c>
+      <c r="E4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F4" t="n">
+        <v>9</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>30.0%</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>UDO_M._MORGAN</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>M. Morgan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>13</v>
+      </c>
+      <c r="E5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F5" t="n">
+        <v>9</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>23.1%</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>46.4%</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>UDO_P._NIXON</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>P. Nixon</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>10</v>
+      </c>
+      <c r="E6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F6" t="n">
+        <v>6</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>35.7%</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>2</v>
+      </c>
+      <c r="K6" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:A2"/>
+  <autoFilter ref="A1:K6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -717,7 +995,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="38" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -740,7 +1018,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Maior volume: M. Morgan (13 L)</t>
+          <t>Maior volume: M. Morgan (28 L)</t>
         </is>
       </c>
     </row>
@@ -752,7 +1030,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Maior volume 3pt: M. Morgan (7 3PA)</t>
+          <t>Maior volume 3pt: M. Morgan (15 3PA)</t>
         </is>
       </c>
     </row>
@@ -764,7 +1042,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Mais eficaz: G. Powell (1.4 pts/shot)</t>
+          <t>Mais eficaz: S. Victo (1.3 pts/shot)</t>
         </is>
       </c>
     </row>
@@ -776,7 +1054,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Zona mais usada: Paint Non-RA (26 L)</t>
+          <t>Zona mais usada: Paint Non-RA (45 L)</t>
         </is>
       </c>
     </row>
@@ -788,7 +1066,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Zona mais eficaz: Paint Non-RA (65.4%)</t>
+          <t>Zona mais eficaz: Mid-Range (61.5%)</t>
         </is>
       </c>
     </row>
@@ -804,7 +1082,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S10"/>
+  <dimension ref="A1:S12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -937,46 +1215,46 @@
         </is>
       </c>
       <c r="C2" t="n">
+        <v>28</v>
+      </c>
+      <c r="D2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E2" t="n">
+        <v>24</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>35.7%</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>26.7%</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>53.6%</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
         <v>13</v>
       </c>
-      <c r="D2" t="n">
-        <v>4</v>
-      </c>
-      <c r="E2" t="n">
-        <v>10</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>30.8%</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>7</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>28.6%</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>53.8%</t>
-        </is>
-      </c>
-      <c r="J2" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="L2" t="n">
-        <v>7</v>
-      </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -985,7 +1263,7 @@
         </is>
       </c>
       <c r="O2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
@@ -996,7 +1274,7 @@
         <v>1</v>
       </c>
       <c r="R2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -1014,34 +1292,34 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="D3" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E3" t="n">
+        <v>20</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>32.1%</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
         <v>11</v>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>41.7%</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
-        <v>3</v>
-      </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>18.2%</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>39.3%</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -1049,184 +1327,184 @@
         </is>
       </c>
       <c r="L3" t="n">
+        <v>11</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>36.4%</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="O3" t="n">
+        <v>10</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>1</v>
+      </c>
+      <c r="R3" t="n">
         <v>7</v>
       </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>42.9%</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="O3" t="n">
-        <v>3</v>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
-      <c r="Q3" t="n">
+      <c r="S3" t="n">
         <v>2</v>
-      </c>
-      <c r="R3" t="n">
-        <v>3</v>
-      </c>
-      <c r="S3" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>UDO_G._POWELL</t>
+          <t>UDO_C._RODGER</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>G. Powell</t>
+          <t>C. Rodger</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E4" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>6</v>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Mid-Range</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="O4" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="Q4" t="n">
         <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S4" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>UDO_C._RODGER</t>
+          <t>UDO_G._POWELL</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>C. Rodger</t>
+          <t>G. Powell</t>
         </is>
       </c>
       <c r="C5" t="n">
+        <v>15</v>
+      </c>
+      <c r="D5" t="n">
+        <v>7</v>
+      </c>
+      <c r="E5" t="n">
+        <v>17</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>46.7%</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
         <v>10</v>
       </c>
-      <c r="D5" t="n">
-        <v>6</v>
-      </c>
-      <c r="E5" t="n">
-        <v>12</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>60.0%</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>30.0%</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Mid-Range</t>
         </is>
       </c>
       <c r="O5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R5" t="n">
         <v>2</v>
       </c>
       <c r="S5" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -1241,98 +1519,98 @@
         </is>
       </c>
       <c r="C6" t="n">
+        <v>15</v>
+      </c>
+      <c r="D6" t="n">
+        <v>6</v>
+      </c>
+      <c r="E6" t="n">
+        <v>14</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
         <v>8</v>
       </c>
-      <c r="D6" t="n">
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>53.3%</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>6</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="O6" t="n">
         <v>4</v>
       </c>
-      <c r="E6" t="n">
-        <v>9</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
-        <v>5</v>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>20.0%</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>62.5%</t>
-        </is>
-      </c>
-      <c r="J6" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>Corner 3 Right</t>
-        </is>
-      </c>
-      <c r="L6" t="n">
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
         <v>4</v>
       </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>25.0%</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="O6" t="n">
-        <v>3</v>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="Q6" t="n">
-        <v>5</v>
-      </c>
       <c r="R6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>UDO_S._VICTO</t>
+          <t>UDO_J._ARAMBURU</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>S. Victo</t>
+          <t>J. Aramburu</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E7" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>85.7%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -1341,75 +1619,75 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>1.7</v>
+        <v>0.8</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>80.0%</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Mid-Range</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="O7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="Q7" t="n">
         <v>6</v>
       </c>
       <c r="R7" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="S7" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>UDO_J._ARAMBURU</t>
+          <t>UDO_S._VICTO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>J. Aramburu</t>
+          <t>S. Victo</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E8" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>63.6%</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -1418,11 +1696,11 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>9.1%</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1430,11 +1708,11 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>80.0%</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1443,67 +1721,67 @@
         </is>
       </c>
       <c r="O8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="Q8" t="n">
         <v>7</v>
       </c>
       <c r="R8" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="S8" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>UDO_D._ARAUJO</t>
+          <t>UDO_T._DIAS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>D. Araujo</t>
+          <t>T. Dias</t>
         </is>
       </c>
       <c r="C9" t="n">
+        <v>7</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E9" t="n">
         <v>4</v>
       </c>
-      <c r="D9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E9" t="n">
-        <v>3</v>
-      </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Corner 3 Left</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="L9" t="n">
@@ -1516,11 +1794,11 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Corner 3 Right</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="O9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P9" t="inlineStr">
         <is>
@@ -1531,77 +1809,231 @@
         <v>8</v>
       </c>
       <c r="R9" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="S9" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>UDO_T._DIAS</t>
+          <t>UDO_C._SA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>T. Dias</t>
+          <t>C. Sa</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>16.7%</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>3</v>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="O10" t="n">
         <v>2</v>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="G10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="J10" t="n">
-        <v>2</v>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="L10" t="n">
-        <v>1</v>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
       <c r="Q10" t="n">
         <v>9</v>
       </c>
       <c r="R10" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="S10" t="n">
         <v>8</v>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>UDO_D._ARAUJO</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>D. Araujo</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>4</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" t="n">
+        <v>3</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>4</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Corner 3 Left</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>3</v>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Corner 3 Right</t>
+        </is>
+      </c>
+      <c r="O11" t="n">
+        <v>1</v>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>10</v>
+      </c>
+      <c r="R11" t="n">
+        <v>8</v>
+      </c>
+      <c r="S11" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>UDO_R._CORREIA</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>R. Correia</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" t="n">
+        <v>2</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>2</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="n">
+        <v>11</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:S10"/>
+  <autoFilter ref="A1:S12"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1612,10 +2044,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S5"/>
+  <dimension ref="A1:S8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
@@ -1736,190 +2168,192 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>UDO_G._POWELL</t>
+          <t>UDO_S._VICTO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>G. Powell</t>
+          <t>S. Victo</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>63.6%</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G2" t="n">
         <v>14</v>
       </c>
       <c r="H2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>9.1%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>80.0%</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Mid-Range</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="O2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="Q2" t="n">
         <v>1</v>
       </c>
       <c r="R2" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>UDO_C._RODGER</t>
+          <t>UDO_G._POWELL</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>C. Rodger</t>
+          <t>G. Powell</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>46.7%</t>
         </is>
       </c>
       <c r="E3" t="n">
+        <v>15</v>
+      </c>
+      <c r="F3" t="n">
+        <v>7</v>
+      </c>
+      <c r="G3" t="n">
+        <v>17</v>
+      </c>
+      <c r="H3" t="n">
         <v>10</v>
       </c>
-      <c r="F3" t="n">
-        <v>6</v>
-      </c>
-      <c r="G3" t="n">
-        <v>12</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>30.0%</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Mid-Range</t>
         </is>
       </c>
       <c r="O3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="Q3" t="n">
         <v>2</v>
       </c>
       <c r="R3" t="n">
-        <v>3</v>
-      </c>
-      <c r="S3" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>UDO_P._NIXON</t>
+          <t>UDO_C._RODGER</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>P. Nixon</t>
+          <t>C. Rodger</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F4" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G4" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="H4" t="n">
-        <v>3</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1928,115 +2362,344 @@
         </is>
       </c>
       <c r="L4" t="n">
+        <v>8</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="O4" t="n">
         <v>7</v>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>42.9%</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="O4" t="n">
-        <v>3</v>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>33.3%</t>
         </is>
       </c>
       <c r="Q4" t="n">
         <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>2</v>
-      </c>
-      <c r="S4" t="n">
-        <v>1</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="S4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>UDO_M._MORGAN</t>
+          <t>UDO_J._TURNER</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>M. Morgan</t>
+          <t>J. Turner</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>30.8%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F5" t="n">
+        <v>6</v>
+      </c>
+      <c r="G5" t="n">
+        <v>14</v>
+      </c>
+      <c r="H5" t="n">
+        <v>8</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>53.3%</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>6</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="O5" t="n">
         <v>4</v>
       </c>
-      <c r="G5" t="n">
-        <v>10</v>
-      </c>
-      <c r="H5" t="n">
-        <v>7</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>28.6%</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>53.8%</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="L5" t="n">
-        <v>7</v>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>28.6%</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="O5" t="n">
-        <v>3</v>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="Q5" t="n">
         <v>4</v>
       </c>
       <c r="R5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="S5" t="n">
         <v>3</v>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>UDO_M._MORGAN</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>M. Morgan</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>35.7%</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>28</v>
+      </c>
+      <c r="F6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G6" t="n">
+        <v>24</v>
+      </c>
+      <c r="H6" t="n">
+        <v>15</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>26.7%</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>53.6%</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>13</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>23.1%</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="O6" t="n">
+        <v>6</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>5</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1</v>
+      </c>
+      <c r="S6" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>UDO_J._ARAMBURU</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>J. Aramburu</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>41.7%</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>12</v>
+      </c>
+      <c r="F7" t="n">
+        <v>5</v>
+      </c>
+      <c r="G7" t="n">
+        <v>10</v>
+      </c>
+      <c r="H7" t="n">
+        <v>5</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>41.7%</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>5</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>80.0%</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="O7" t="n">
+        <v>3</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>6</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>UDO_P._NIXON</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>P. Nixon</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>32.1%</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>28</v>
+      </c>
+      <c r="F8" t="n">
+        <v>9</v>
+      </c>
+      <c r="G8" t="n">
+        <v>20</v>
+      </c>
+      <c r="H8" t="n">
+        <v>11</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>18.2%</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>39.3%</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>11</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>36.4%</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="O8" t="n">
+        <v>10</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>7</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1</v>
+      </c>
+      <c r="S8" t="n">
+        <v>4</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:S5"/>
+  <autoFilter ref="A1:S8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2047,7 +2710,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N10"/>
+  <dimension ref="A1:N12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -2150,178 +2813,178 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="D2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>26.7%</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>53.6%</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>28</v>
+      </c>
+      <c r="H2" t="n">
+        <v>24</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>13</v>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>23.1%</t>
+        </is>
+      </c>
+      <c r="M2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N2" t="n">
         <v>2</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>28.6%</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>53.8%</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>13</v>
-      </c>
-      <c r="H2" t="n">
-        <v>10</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="K2" t="n">
-        <v>7</v>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>28.6%</t>
-        </is>
-      </c>
-      <c r="M2" t="n">
-        <v>1</v>
-      </c>
-      <c r="N2" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>UDO_G._POWELL</t>
+          <t>UDO_P._NIXON</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>G. Powell</t>
+          <t>P. Nixon</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D3" t="n">
         <v>2</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>18.2%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>39.3%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="H3" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="I3" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>36.4%</t>
         </is>
       </c>
       <c r="M3" t="n">
         <v>2</v>
       </c>
       <c r="N3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>UDO_J._TURNER</t>
+          <t>UDO_G._POWELL</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>J. Turner</t>
+          <t>G. Powell</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="H4" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="I4" t="n">
         <v>1.1</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Corner 3 Right</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="M4" t="n">
         <v>3</v>
       </c>
       <c r="N4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>UDO_D._ARAUJO</t>
+          <t>UDO_J._TURNER</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>D. Araujo</t>
+          <t>J. Turner</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -2330,163 +2993,163 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="H5" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Corner 3 Left</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="M5" t="n">
         <v>4</v>
       </c>
       <c r="N5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>UDO_P._NIXON</t>
+          <t>UDO_J._ARAMBURU</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>P. Nixon</t>
+          <t>J. Aramburu</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="G6" t="n">
         <v>12</v>
       </c>
       <c r="H6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I6" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>80.0%</t>
         </is>
       </c>
       <c r="M6" t="n">
         <v>5</v>
       </c>
       <c r="N6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>UDO_J._ARAMBURU</t>
+          <t>UDO_D._ARAUJO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>J. Aramburu</t>
+          <t>D. Araujo</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>4</v>
+      </c>
+      <c r="H7" t="n">
+        <v>3</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Corner 3 Left</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>3</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
           <t>33.3%</t>
-        </is>
-      </c>
-      <c r="G7" t="n">
-        <v>6</v>
-      </c>
-      <c r="H7" t="n">
-        <v>4</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="K7" t="n">
-        <v>2</v>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>50.0%</t>
         </is>
       </c>
       <c r="M7" t="n">
         <v>6</v>
       </c>
       <c r="N7" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>UDO_S._VICTO</t>
+          <t>UDO_T._DIAS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>S. Victo</t>
+          <t>T. Dias</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -2498,17 +3161,17 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="G8" t="n">
         <v>7</v>
       </c>
       <c r="H8" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I8" t="n">
-        <v>1.7</v>
+        <v>0.6</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -2516,11 +3179,11 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="M8" t="n">
@@ -2533,34 +3196,38 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>UDO_C._RODGER</t>
+          <t>UDO_S._VICTO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>C. Rodger</t>
+          <t>S. Victo</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
       </c>
-      <c r="E9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>9.1%</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H9" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I9" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -2568,49 +3235,55 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>80.0%</t>
         </is>
       </c>
       <c r="M9" t="n">
         <v>8</v>
       </c>
-      <c r="N9" t="inlineStr"/>
+      <c r="N9" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>UDO_T._DIAS</t>
+          <t>UDO_C._SA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>T. Dias</t>
+          <t>C. Sa</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
       </c>
-      <c r="E10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I10" t="n">
-        <v>2</v>
+        <v>0.7</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -2618,20 +3291,122 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="M10" t="n">
         <v>8</v>
       </c>
-      <c r="N10" t="inlineStr"/>
+      <c r="N10" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>UDO_C._RODGER</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>C. Rodger</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>16</v>
+      </c>
+      <c r="H11" t="n">
+        <v>16</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>8</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="M11" t="n">
+        <v>10</v>
+      </c>
+      <c r="N11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>UDO_R._CORREIA</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>R. Correia</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" t="n">
+        <v>2</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>1</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="M12" t="n">
+        <v>10</v>
+      </c>
+      <c r="N12" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N10"/>
+  <autoFilter ref="A1:N12"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2642,28 +3417,267 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:N4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="19" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="19" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="19" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>player_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>player_name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>fg3a</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>fg3m</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>fg3_pct</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>three_rate</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>shot_attempts</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>points_from_shots</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>pts_per_shot</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>top_zone_1</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>top_zone_1_att</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>top_zone_1_pct</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>team_rank_3pt_volume</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>team_rank_3pt_pct</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>sem dados</t>
-        </is>
+          <t>UDO_G._POWELL</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>G. Powell</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>10</v>
+      </c>
+      <c r="D2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>30.0%</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H2" t="n">
+        <v>17</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>10</v>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>30.0%</t>
+        </is>
+      </c>
+      <c r="M2" t="n">
+        <v>3</v>
+      </c>
+      <c r="N2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>UDO_M._MORGAN</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>M. Morgan</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>15</v>
+      </c>
+      <c r="D3" t="n">
+        <v>4</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>26.7%</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>53.6%</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>28</v>
+      </c>
+      <c r="H3" t="n">
+        <v>24</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>13</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>23.1%</t>
+        </is>
+      </c>
+      <c r="M3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>UDO_P._NIXON</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>P. Nixon</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>11</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>18.2%</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>39.3%</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>28</v>
+      </c>
+      <c r="H4" t="n">
+        <v>20</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>11</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>36.4%</t>
+        </is>
+      </c>
+      <c r="M4" t="n">
+        <v>2</v>
+      </c>
+      <c r="N4" t="n">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:A2"/>
+  <autoFilter ref="A1:N4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2742,32 +3756,32 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="C2" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="D2" t="n">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>65.4%</t>
+          <t>48.9%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>36.6%</t>
+          <t>31.5%</t>
         </is>
       </c>
       <c r="H2" t="n">
         <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -2777,32 +3791,32 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>20.9%</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>28.2%</t>
+          <t>30.1%</t>
         </is>
       </c>
       <c r="H3" t="n">
         <v>2</v>
       </c>
       <c r="I3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -2812,25 +3826,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="C4" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D4" t="n">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>14.1%</t>
+          <t>19.6%</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -2847,25 +3861,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C5" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D5" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>71.4%</t>
+          <t>61.5%</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>9.1%</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -2882,32 +3896,32 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>7.0%</t>
+          <t>6.3%</t>
         </is>
       </c>
       <c r="H6" t="n">
         <v>5</v>
       </c>
       <c r="I6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
@@ -2917,7 +3931,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C7" t="n">
         <v>1</v>
@@ -2927,22 +3941,22 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="H7" t="n">
         <v>6</v>
       </c>
       <c r="I7" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -2957,7 +3971,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P10"/>
+  <dimension ref="A1:P12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -2968,7 +3982,7 @@
     <col width="19" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="19" customWidth="1" min="9" max="9"/>
+    <col width="17" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="16" customWidth="1" min="12" max="12"/>
@@ -3077,11 +4091,11 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -3090,7 +4104,7 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -3099,35 +4113,35 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Mid-Range</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>30.8%</t>
+          <t>35.7%</t>
         </is>
       </c>
       <c r="N2" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="3">
@@ -3147,11 +4161,11 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>36.4%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -3160,180 +4174,180 @@
         </is>
       </c>
       <c r="G3" t="n">
+        <v>10</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
         <v>3</v>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Mid-Range</t>
-        </is>
-      </c>
-      <c r="J3" t="n">
-        <v>1</v>
-      </c>
       <c r="K3" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>32.1%</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>18.2%</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>UDO_G._POWELL</t>
+          <t>UDO_C._RODGER</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>G. Powell</t>
+          <t>C. Rodger</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>7</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>42.9%</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
           <t>Mid-Range</t>
         </is>
       </c>
-      <c r="G4" t="n">
-        <v>2</v>
-      </c>
-      <c r="H4" t="inlineStr">
+      <c r="J4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="J4" t="n">
-        <v>1</v>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
       <c r="L4" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>6</v>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="O4" t="inlineStr"/>
       <c r="P4" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>UDO_C._RODGER</t>
+          <t>UDO_G._POWELL</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>C. Rodger</t>
+          <t>G. Powell</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>10</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>30.0%</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
           <t>Paint Non-RA</t>
         </is>
       </c>
-      <c r="D5" t="n">
-        <v>6</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>66.7%</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
-        <v>3</v>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Mid-Range</t>
-        </is>
-      </c>
       <c r="J5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="L5" t="n">
+        <v>15</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>46.7%</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
         <v>10</v>
       </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>60.0%</t>
-        </is>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="inlineStr"/>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>30.0%</t>
+        </is>
+      </c>
       <c r="P5" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="6">
@@ -3349,123 +4363,123 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>6</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>4</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
           <t>Corner 3 Right</t>
         </is>
       </c>
-      <c r="D6" t="n">
+      <c r="J6" t="n">
         <v>4</v>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>25.0%</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
-        <v>3</v>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="J6" t="n">
-        <v>1</v>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
       <c r="L6" t="n">
+        <v>15</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="N6" t="n">
         <v>8</v>
       </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="N6" t="n">
-        <v>5</v>
-      </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>UDO_S._VICTO</t>
+          <t>UDO_J._ARAMBURU</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>S. Victo</t>
+          <t>J. Aramburu</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>5</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>80.0%</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>3</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
           <t>Paint Non-RA</t>
         </is>
       </c>
-      <c r="D7" t="n">
-        <v>4</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Mid-Range</t>
-        </is>
-      </c>
-      <c r="G7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
       <c r="J7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>85.7%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -3473,18 +4487,18 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1.7</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>UDO_J._ARAMBURU</t>
+          <t>UDO_S._VICTO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>J. Aramburu</t>
+          <t>S. Victo</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -3493,11 +4507,11 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>80.0%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -3506,16 +4520,16 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Mid-Range</t>
         </is>
       </c>
       <c r="J8" t="n">
@@ -3523,43 +4537,43 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>11</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>63.6%</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="L8" t="n">
-        <v>6</v>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
-      <c r="N8" t="n">
-        <v>2</v>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
       <c r="P8" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>UDO_D._ARAUJO</t>
+          <t>UDO_T._DIAS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>D. Araujo</t>
+          <t>T. Dias</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Corner 3 Left</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -3572,49 +4586,59 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Corner 3 Right</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
       <c r="L9" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="N9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>UDO_T._DIAS</t>
+          <t>UDO_C._SA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>T. Dias</t>
+          <t>C. Sa</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -3623,37 +4647,167 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>2</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Corner 3 Left</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>6</v>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="N10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>UDO_D._ARAUJO</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>D. Araujo</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Corner 3 Left</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>3</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Corner 3 Right</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="n">
+        <v>4</v>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="N11" t="n">
+        <v>4</v>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>UDO_R._CORREIA</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>R. Correia</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="n">
-        <v>1</v>
-      </c>
-      <c r="M10" t="inlineStr">
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="N10" t="n">
+      <c r="N12" t="n">
         <v>0</v>
       </c>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="n">
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="n">
         <v>2</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P10"/>
+  <autoFilter ref="A1:P12"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3664,10 +4818,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:K11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="19" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
@@ -3740,84 +4894,84 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>UDO_P._NIXON</t>
+          <t>UDO_M._MORGAN</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>P. Nixon</t>
+          <t>M. Morgan</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E2" t="n">
         <v>3</v>
       </c>
       <c r="F2" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>58.3%</t>
+          <t>46.4%</t>
         </is>
       </c>
       <c r="J2" t="n">
         <v>1</v>
       </c>
       <c r="K2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>UDO_M._MORGAN</t>
+          <t>UDO_P._NIXON</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>M. Morgan</t>
+          <t>P. Nixon</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>36.4%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>53.8%</t>
+          <t>39.3%</t>
         </is>
       </c>
       <c r="J3" t="n">
@@ -3830,39 +4984,39 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>UDO_C._RODGER</t>
+          <t>UDO_G._POWELL</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>C. Rodger</t>
+          <t>G. Powell</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
+          <t>30.0%</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
           <t>66.7%</t>
-        </is>
-      </c>
-      <c r="H4" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>60.0%</t>
         </is>
       </c>
       <c r="J4" t="n">
@@ -3875,12 +5029,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>UDO_G._POWELL</t>
+          <t>UDO_P._NIXON</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>G. Powell</t>
+          <t>P. Nixon</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -3889,7 +5043,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E5" t="n">
         <v>2</v>
@@ -3899,26 +5053,296 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>35.7%</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>2</v>
+      </c>
+      <c r="K5" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>UDO_C._RODGER</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>C. Rodger</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>8</v>
+      </c>
+      <c r="E6" t="n">
+        <v>4</v>
+      </c>
+      <c r="F6" t="n">
+        <v>8</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>UDO_C._RODGER</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>C. Rodger</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>7</v>
+      </c>
+      <c r="E7" t="n">
+        <v>3</v>
+      </c>
+      <c r="F7" t="n">
+        <v>6</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>42.9%</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>43.8%</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>2</v>
+      </c>
+      <c r="K7" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>UDO_J._TURNER</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>J. Turner</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>6</v>
+      </c>
+      <c r="E8" t="n">
+        <v>4</v>
+      </c>
+      <c r="F8" t="n">
+        <v>8</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>UDO_M._MORGAN</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>M. Morgan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>6</v>
+      </c>
+      <c r="E9" t="n">
+        <v>2</v>
+      </c>
+      <c r="F9" t="n">
+        <v>4</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
           <t>33.3%</t>
         </is>
       </c>
-      <c r="H5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>60.0%</t>
-        </is>
-      </c>
-      <c r="J5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K5" t="n">
+      <c r="H9" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>21.4%</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>2</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>UDO_J._ARAMBURU</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>J. Aramburu</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>5</v>
+      </c>
+      <c r="E10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F10" t="n">
+        <v>8</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>80.0%</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>41.7%</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>UDO_S._VICTO</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>S. Victo</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>5</v>
+      </c>
+      <c r="E11" t="n">
+        <v>4</v>
+      </c>
+      <c r="F11" t="n">
+        <v>8</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>80.0%</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>45.5%</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K5"/>
+  <autoFilter ref="A1:K11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/site/leagues/betclic/2026_2027/xlsx/shot_packs/shot_pack_UDO.xlsx
+++ b/site/leagues/betclic/2026_2027/xlsx/shot_packs/shot_pack_UDO.xlsx
@@ -21,14 +21,14 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'overview'!$A$1:$W$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'alerts'!$A$1:$B$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'players_volume'!$A$1:$S$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'players_eff'!$A$1:$S$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'players_3pt_volume'!$A$1:$N$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'players_3pt_pct'!$A$1:$N$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'players_volume'!$A$1:$S$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'players_eff'!$A$1:$S$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'players_3pt_volume'!$A$1:$N$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'players_3pt_pct'!$A$1:$N$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'team_zones'!$A$1:$I$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'preferred_areas'!$A$1:$P$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'player_zones_volume'!$A$1:$K$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'player_zones_pct'!$A$1:$K$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'preferred_areas'!$A$1:$P$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'player_zones_volume'!$A$1:$K$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'player_zones_pct'!$A$1:$K$9</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -448,10 +448,10 @@
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="19" customWidth="1" min="13" max="13"/>
     <col width="16" customWidth="1" min="14" max="14"/>
     <col width="16" customWidth="1" min="15" max="15"/>
-    <col width="19" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
     <col width="16" customWidth="1" min="17" max="17"/>
     <col width="16" customWidth="1" min="18" max="18"/>
     <col width="25" customWidth="1" min="19" max="19"/>
@@ -590,83 +590,83 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>143</v>
+        <v>219</v>
       </c>
       <c r="D2" t="n">
-        <v>58</v>
+        <v>98</v>
       </c>
       <c r="E2" t="n">
-        <v>128</v>
+        <v>219</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>40.6%</t>
+          <t>44.7%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>86</v>
+        <v>131</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>53.5%</t>
+          <t>57.3%</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>57</v>
+        <v>88</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>21.1%</t>
+          <t>26.1%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>39.9%</t>
+          <t>40.2%</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="N2" t="n">
+        <v>67</v>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>26.9%</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
           <t>Paint Non-RA</t>
         </is>
       </c>
-      <c r="N2" t="n">
-        <v>45</v>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>48.9%</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
       <c r="Q2" t="n">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20.9%</t>
+          <t>47.5%</t>
         </is>
       </c>
       <c r="S2" t="n">
         <v>11</v>
       </c>
       <c r="T2" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="U2" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="V2" t="n">
         <v>11</v>
       </c>
       <c r="W2" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -681,10 +681,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:K9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="19" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
@@ -757,35 +757,35 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>UDO_C._RODGER</t>
+          <t>UDO_J._ARAMBURU</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>C. Rodger</t>
+          <t>J. Aramburu</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="D2" t="n">
+        <v>9</v>
+      </c>
+      <c r="E2" t="n">
         <v>8</v>
       </c>
-      <c r="E2" t="n">
-        <v>4</v>
-      </c>
       <c r="F2" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>88.9%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -802,12 +802,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>UDO_P._NIXON</t>
+          <t>UDO_C._RODGER</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>P. Nixon</t>
+          <t>C. Rodger</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -819,26 +819,26 @@
         <v>11</v>
       </c>
       <c r="E3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F3" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>39.3%</t>
+          <t>40.7%</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K3" t="n">
         <v>1</v>
@@ -847,88 +847,88 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>UDO_G._POWELL</t>
+          <t>UDO_C._RODGER</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>G. Powell</t>
+          <t>C. Rodger</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E4" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F4" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>51.9%</t>
         </is>
       </c>
       <c r="J4" t="n">
         <v>1</v>
       </c>
       <c r="K4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>UDO_M._MORGAN</t>
+          <t>UDO_P._NIXON</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>M. Morgan</t>
+          <t>P. Nixon</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>13</v>
       </c>
       <c r="E5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>46.4%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K5" t="n">
         <v>2</v>
@@ -937,50 +937,185 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>UDO_G._POWELL</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>G. Powell</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>17</v>
+      </c>
+      <c r="E6" t="n">
+        <v>6</v>
+      </c>
+      <c r="F6" t="n">
+        <v>18</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>35.3%</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>68.0%</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>UDO_M._MORGAN</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>M. Morgan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>9</v>
+      </c>
+      <c r="E7" t="n">
+        <v>3</v>
+      </c>
+      <c r="F7" t="n">
+        <v>6</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>2</v>
+      </c>
+      <c r="K7" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>UDO_M._MORGAN</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>M. Morgan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E8" t="n">
+        <v>4</v>
+      </c>
+      <c r="F8" t="n">
+        <v>12</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>26.7%</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>41.7%</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>UDO_P._NIXON</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>P. Nixon</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>Above the Break 3</t>
         </is>
       </c>
-      <c r="D6" t="n">
-        <v>10</v>
-      </c>
-      <c r="E6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F6" t="n">
-        <v>6</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>20.0%</t>
-        </is>
-      </c>
-      <c r="H6" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>35.7%</t>
-        </is>
-      </c>
-      <c r="J6" t="n">
-        <v>2</v>
-      </c>
-      <c r="K6" t="n">
-        <v>2</v>
+      <c r="D9" t="n">
+        <v>15</v>
+      </c>
+      <c r="E9" t="n">
+        <v>4</v>
+      </c>
+      <c r="F9" t="n">
+        <v>12</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>26.7%</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>38.5%</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K6"/>
+  <autoFilter ref="A1:K9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -995,7 +1130,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="38" customWidth="1" min="2" max="2"/>
+    <col width="43" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1018,7 +1153,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Maior volume: M. Morgan (28 L)</t>
+          <t>Maior volume: P. Nixon (39 L)</t>
         </is>
       </c>
     </row>
@@ -1030,7 +1165,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Maior volume 3pt: M. Morgan (15 3PA)</t>
+          <t>Maior volume 3pt: G. Powell (18 3PA)</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1177,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Mais eficaz: S. Victo (1.3 pts/shot)</t>
+          <t>Mais eficaz: G. Powell (1.2 pts/shot)</t>
         </is>
       </c>
     </row>
@@ -1054,7 +1189,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Zona mais usada: Paint Non-RA (45 L)</t>
+          <t>Zona mais usada: Above the Break 3 (67 L)</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1201,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Zona mais eficaz: Mid-Range (61.5%)</t>
+          <t>Zona mais eficaz: Restricted Area (66.1%)</t>
         </is>
       </c>
     </row>
@@ -1082,7 +1217,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S12"/>
+  <dimension ref="A1:S13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -1206,39 +1341,39 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>UDO_M._MORGAN</t>
+          <t>UDO_P._NIXON</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>M. Morgan</t>
+          <t>P. Nixon</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="D2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E2" t="n">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>35.7%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>26.7%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>53.6%</t>
+          <t>43.6%</t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -1250,111 +1385,111 @@
         </is>
       </c>
       <c r="L2" t="n">
+        <v>15</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>26.7%</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="O2" t="n">
         <v>13</v>
       </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>23.1%</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="O2" t="n">
-        <v>6</v>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="Q2" t="n">
         <v>1</v>
       </c>
       <c r="R2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>UDO_P._NIXON</t>
+          <t>UDO_M._MORGAN</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>P. Nixon</t>
+          <t>M. Morgan</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="D3" t="n">
+        <v>14</v>
+      </c>
+      <c r="E3" t="n">
+        <v>33</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>38.9%</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>18</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>27.8%</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>15</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>26.7%</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="O3" t="n">
         <v>9</v>
       </c>
-      <c r="E3" t="n">
-        <v>20</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>32.1%</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
-        <v>11</v>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>18.2%</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>39.3%</t>
-        </is>
-      </c>
-      <c r="J3" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="L3" t="n">
-        <v>11</v>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>36.4%</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="O3" t="n">
-        <v>10</v>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="S3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -1369,17 +1504,17 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="D4" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E4" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>51.9%</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1396,192 +1531,192 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>14</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
           <t>Paint Non-RA</t>
         </is>
       </c>
-      <c r="L4" t="n">
-        <v>8</v>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
       <c r="O4" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="Q4" t="n">
         <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>UDO_G._POWELL</t>
+          <t>UDO_J._TURNER</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>G. Powell</t>
+          <t>J. Turner</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="D5" t="n">
+        <v>13</v>
+      </c>
+      <c r="E5" t="n">
+        <v>30</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>12</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>46.2%</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
         <v>7</v>
       </c>
-      <c r="E5" t="n">
-        <v>17</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>46.7%</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
-        <v>10</v>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>30.0%</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>66.7%</t>
-        </is>
-      </c>
-      <c r="J5" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="L5" t="n">
-        <v>10</v>
-      </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Mid-Range</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="O5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>83.3%</t>
         </is>
       </c>
       <c r="Q5" t="n">
         <v>4</v>
       </c>
       <c r="R5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>UDO_J._TURNER</t>
+          <t>UDO_G._POWELL</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>J. Turner</t>
+          <t>G. Powell</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="D6" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E6" t="n">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>48.0%</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>72.0%</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>17</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>35.3%</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
           <t>Paint Non-RA</t>
         </is>
       </c>
-      <c r="L6" t="n">
-        <v>6</v>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>66.7%</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
       <c r="O6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="S6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -1596,66 +1731,66 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="D7" t="n">
+        <v>10</v>
+      </c>
+      <c r="E7" t="n">
+        <v>21</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>55.6%</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>7</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>14.3%</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>38.9%</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>9</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>88.9%</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="O7" t="n">
         <v>5</v>
       </c>
-      <c r="E7" t="n">
-        <v>10</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>41.7%</t>
-        </is>
-      </c>
-      <c r="G7" t="n">
-        <v>5</v>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>41.7%</t>
-        </is>
-      </c>
-      <c r="J7" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="L7" t="n">
-        <v>5</v>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>80.0%</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="O7" t="n">
-        <v>3</v>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="Q7" t="n">
         <v>6</v>
       </c>
       <c r="R7" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1673,34 +1808,34 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D8" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E8" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>63.6%</t>
+          <t>58.8%</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>9.1%</t>
+          <t>17.6%</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1708,11 +1843,11 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>83.3%</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1721,51 +1856,51 @@
         </is>
       </c>
       <c r="O8" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="Q8" t="n">
         <v>7</v>
       </c>
       <c r="R8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>UDO_T._DIAS</t>
+          <t>UDO_C._SA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>T. Dias</t>
+          <t>C. Sa</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E9" t="n">
+        <v>8</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
         <v>4</v>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>28.6%</t>
-        </is>
-      </c>
-      <c r="G9" t="n">
-        <v>2</v>
-      </c>
       <c r="H9" t="inlineStr">
         <is>
           <t>0.0%</t>
@@ -1773,11 +1908,11 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1785,64 +1920,64 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="O9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="Q9" t="n">
         <v>8</v>
       </c>
       <c r="R9" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="S9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>UDO_C._SA</t>
+          <t>UDO_T._DIAS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>C. Sa</t>
+          <t>T. Dias</t>
         </is>
       </c>
       <c r="C10" t="n">
+        <v>11</v>
+      </c>
+      <c r="D10" t="n">
+        <v>3</v>
+      </c>
+      <c r="E10" t="n">
         <v>6</v>
       </c>
-      <c r="D10" t="n">
-        <v>2</v>
-      </c>
-      <c r="E10" t="n">
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>27.3%</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
         <v>4</v>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
-      <c r="G10" t="n">
-        <v>1</v>
-      </c>
       <c r="H10" t="inlineStr">
         <is>
           <t>0.0%</t>
@@ -1850,46 +1985,46 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>36.4%</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="O10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="Q10" t="n">
         <v>9</v>
       </c>
       <c r="R10" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="S10" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11">
@@ -1963,7 +2098,7 @@
         <v>10</v>
       </c>
       <c r="R11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="S11" t="n">
         <v>6</v>
@@ -1972,16 +2107,16 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>UDO_R._CORREIA</t>
+          <t>UDO_M._FONSECA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>R. Correia</t>
+          <t>M. Fonseca</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D12" t="n">
         <v>1</v>
@@ -1991,49 +2126,126 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr">
         <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>2</v>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Corner 3 Left</t>
+        </is>
+      </c>
+      <c r="O12" t="n">
+        <v>1</v>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="J12" t="n">
-        <v>2</v>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="L12" t="n">
-        <v>1</v>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr"/>
       <c r="Q12" t="n">
         <v>11</v>
       </c>
       <c r="R12" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>UDO_R._CORREIA</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>R. Correia</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" t="n">
+        <v>2</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>2</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="n">
+        <v>12</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1</v>
+      </c>
+      <c r="S13" t="n">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:S12"/>
+  <autoFilter ref="A1:S13"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2044,7 +2256,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S8"/>
+  <dimension ref="A1:S10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -2168,60 +2380,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>UDO_S._VICTO</t>
+          <t>UDO_G._POWELL</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>S. Victo</t>
+          <t>G. Powell</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>63.6%</t>
+          <t>48.0%</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="F2" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="G2" t="n">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>9.1%</t>
+          <t>72.0%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>17</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>35.3%</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
           <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="L2" t="n">
-        <v>5</v>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>80.0%</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
         </is>
       </c>
       <c r="O2" t="n">
@@ -2229,166 +2441,172 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="Q2" t="n">
         <v>1</v>
       </c>
       <c r="R2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>UDO_G._POWELL</t>
+          <t>UDO_S._VICTO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>G. Powell</t>
+          <t>S. Victo</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>58.8%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F3" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G3" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="H3" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>17.6%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>83.3%</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Mid-Range</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="O3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="Q3" t="n">
         <v>2</v>
       </c>
       <c r="R3" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>UDO_C._RODGER</t>
+          <t>UDO_J._ARAMBURU</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>C. Rodger</t>
+          <t>J. Aramburu</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G4" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="inlineStr"/>
+        <v>7</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>14.3%</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>88.9%</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="O4" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="Q4" t="n">
         <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>3</v>
-      </c>
-      <c r="S4" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="S4" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2402,59 +2620,59 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F5" t="n">
+        <v>13</v>
+      </c>
+      <c r="G5" t="n">
+        <v>30</v>
+      </c>
+      <c r="H5" t="n">
+        <v>12</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>46.2%</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>7</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>57.1%</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="O5" t="n">
         <v>6</v>
       </c>
-      <c r="G5" t="n">
-        <v>14</v>
-      </c>
-      <c r="H5" t="n">
-        <v>8</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>25.0%</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>53.3%</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="L5" t="n">
-        <v>6</v>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>66.7%</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="O5" t="n">
-        <v>4</v>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>83.3%</t>
         </is>
       </c>
       <c r="Q5" t="n">
@@ -2464,61 +2682,57 @@
         <v>4</v>
       </c>
       <c r="S5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>UDO_M._MORGAN</t>
+          <t>UDO_C._RODGER</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>M. Morgan</t>
+          <t>C. Rodger</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>35.7%</t>
+          <t>51.9%</t>
         </is>
       </c>
       <c r="E6" t="n">
+        <v>27</v>
+      </c>
+      <c r="F6" t="n">
+        <v>14</v>
+      </c>
+      <c r="G6" t="n">
         <v>28</v>
       </c>
-      <c r="F6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G6" t="n">
-        <v>24</v>
-      </c>
       <c r="H6" t="n">
-        <v>15</v>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>26.7%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>53.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -2527,98 +2741,96 @@
         </is>
       </c>
       <c r="O6" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="Q6" t="n">
         <v>5</v>
       </c>
       <c r="R6" t="n">
-        <v>1</v>
-      </c>
-      <c r="S6" t="n">
-        <v>2</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="S6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>UDO_J._ARAMBURU</t>
+          <t>UDO_M._MORGAN</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>J. Aramburu</t>
+          <t>M. Morgan</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="F7" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="G7" t="n">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="H7" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="O7" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="Q7" t="n">
         <v>6</v>
       </c>
       <c r="R7" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -2633,59 +2845,59 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>32.1%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="F8" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="G8" t="n">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="H8" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>18.2%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>39.3%</t>
+          <t>43.6%</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>15</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>26.7%</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
           <t>Paint Non-RA</t>
         </is>
       </c>
-      <c r="L8" t="n">
-        <v>11</v>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>36.4%</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
       <c r="O8" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="Q8" t="n">
@@ -2695,11 +2907,165 @@
         <v>1</v>
       </c>
       <c r="S8" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>UDO_C._SA</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>C. Sa</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>12</v>
+      </c>
+      <c r="F9" t="n">
         <v>4</v>
       </c>
+      <c r="G9" t="n">
+        <v>8</v>
+      </c>
+      <c r="H9" t="n">
+        <v>4</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>4</v>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="O9" t="n">
+        <v>4</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>8</v>
+      </c>
+      <c r="R9" t="n">
+        <v>8</v>
+      </c>
+      <c r="S9" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>UDO_T._DIAS</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>T. Dias</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>27.3%</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>11</v>
+      </c>
+      <c r="F10" t="n">
+        <v>3</v>
+      </c>
+      <c r="G10" t="n">
+        <v>6</v>
+      </c>
+      <c r="H10" t="n">
+        <v>4</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>36.4%</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>4</v>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="O10" t="n">
+        <v>4</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>9</v>
+      </c>
+      <c r="R10" t="n">
+        <v>9</v>
+      </c>
+      <c r="S10" t="n">
+        <v>7</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:S8"/>
+  <autoFilter ref="A1:S10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2710,7 +3076,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N12"/>
+  <dimension ref="A1:N13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -2804,38 +3170,38 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>UDO_M._MORGAN</t>
+          <t>UDO_G._POWELL</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>M. Morgan</t>
+          <t>G. Powell</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>26.7%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>53.6%</t>
+          <t>72.0%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="H2" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="I2" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -2843,71 +3209,71 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>35.3%</t>
         </is>
       </c>
       <c r="M2" t="n">
         <v>1</v>
       </c>
       <c r="N2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>UDO_P._NIXON</t>
+          <t>UDO_M._MORGAN</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>P. Nixon</t>
+          <t>M. Morgan</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>18.2%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>39.3%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="H3" t="n">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N3" t="n">
         <v>4</v>
@@ -2916,57 +3282,57 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>UDO_G._POWELL</t>
+          <t>UDO_P._NIXON</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>G. Powell</t>
+          <t>P. Nixon</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="D4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>43.6%</t>
         </is>
       </c>
       <c r="G4" t="n">
+        <v>39</v>
+      </c>
+      <c r="H4" t="n">
+        <v>34</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
         <v>15</v>
       </c>
-      <c r="H4" t="n">
-        <v>17</v>
-      </c>
-      <c r="I4" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="K4" t="n">
-        <v>10</v>
-      </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="M4" t="n">
         <v>3</v>
       </c>
       <c r="N4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
@@ -2981,29 +3347,29 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="H5" t="n">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="I5" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -3011,18 +3377,18 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="M5" t="n">
         <v>4</v>
       </c>
       <c r="N5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -3037,29 +3403,29 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="H6" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -3067,18 +3433,18 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>88.9%</t>
         </is>
       </c>
       <c r="M6" t="n">
         <v>5</v>
       </c>
       <c r="N6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7">
@@ -3134,22 +3500,22 @@
         <v>6</v>
       </c>
       <c r="N7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>UDO_T._DIAS</t>
+          <t>UDO_C._SA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>T. Dias</t>
+          <t>C. Sa</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -3161,51 +3527,51 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="G8" t="n">
+        <v>12</v>
+      </c>
+      <c r="H8" t="n">
+        <v>8</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>4</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="M8" t="n">
+        <v>6</v>
+      </c>
+      <c r="N8" t="n">
         <v>7</v>
-      </c>
-      <c r="H8" t="n">
-        <v>4</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="K8" t="n">
-        <v>3</v>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
-      <c r="M8" t="n">
-        <v>7</v>
-      </c>
-      <c r="N8" t="n">
-        <v>6</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>UDO_S._VICTO</t>
+          <t>UDO_T._DIAS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>S. Victo</t>
+          <t>T. Dias</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -3217,17 +3583,17 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>9.1%</t>
+          <t>36.4%</t>
         </is>
       </c>
       <c r="G9" t="n">
         <v>11</v>
       </c>
       <c r="H9" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="I9" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -3235,115 +3601,119 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="N9" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>UDO_C._SA</t>
+          <t>UDO_S._VICTO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>C. Sa</t>
+          <t>S. Victo</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>17.6%</t>
         </is>
       </c>
       <c r="G10" t="n">
+        <v>17</v>
+      </c>
+      <c r="H10" t="n">
+        <v>21</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
         <v>6</v>
       </c>
-      <c r="H10" t="n">
-        <v>4</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="K10" t="n">
-        <v>3</v>
-      </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>83.3%</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N10" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>UDO_C._RODGER</t>
+          <t>UDO_M._FONSECA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>C. Rodger</t>
+          <t>M. Fonseca</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
-      <c r="E11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="H11" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="I11" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -3353,17 +3723,19 @@
       <c r="M11" t="n">
         <v>10</v>
       </c>
-      <c r="N11" t="inlineStr"/>
+      <c r="N11" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>UDO_R._CORREIA</t>
+          <t>UDO_C._RODGER</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>R. Correia</t>
+          <t>C. Rodger</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -3379,34 +3751,84 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="H12" t="n">
+        <v>28</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>14</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="M12" t="n">
+        <v>11</v>
+      </c>
+      <c r="N12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>UDO_R._CORREIA</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>R. Correia</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" t="n">
         <v>2</v>
       </c>
-      <c r="I12" t="n">
+      <c r="I13" t="n">
         <v>2</v>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>Restricted Area</t>
         </is>
       </c>
-      <c r="K12" t="n">
-        <v>1</v>
-      </c>
-      <c r="L12" t="inlineStr">
+      <c r="K13" t="n">
+        <v>1</v>
+      </c>
+      <c r="L13" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="M12" t="n">
-        <v>10</v>
-      </c>
-      <c r="N12" t="inlineStr"/>
+      <c r="M13" t="n">
+        <v>11</v>
+      </c>
+      <c r="N13" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N12"/>
+  <autoFilter ref="A1:N13"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3417,7 +3839,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N4"/>
+  <dimension ref="A1:N5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -3520,45 +3942,45 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="D2" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>72.0%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="H2" t="n">
+        <v>31</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
         <v>17</v>
       </c>
-      <c r="I2" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="K2" t="n">
-        <v>10</v>
-      </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>35.3%</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N2" t="n">
         <v>1</v>
@@ -3567,54 +3989,54 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>UDO_M._MORGAN</t>
+          <t>UDO_J._TURNER</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>M. Morgan</t>
+          <t>J. Turner</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D3" t="n">
         <v>4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>26.7%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>53.6%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="H3" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="I3" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N3" t="n">
         <v>2</v>
@@ -3623,61 +4045,117 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>UDO_P._NIXON</t>
+          <t>UDO_M._MORGAN</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>P. Nixon</t>
+          <t>M. Morgan</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>18.2%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>39.3%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="H4" t="n">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N4" t="n">
         <v>4</v>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>UDO_P._NIXON</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>P. Nixon</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>17</v>
+      </c>
+      <c r="D5" t="n">
+        <v>4</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>23.5%</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>43.6%</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>39</v>
+      </c>
+      <c r="H5" t="n">
+        <v>34</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>15</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>26.7%</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
+        <v>3</v>
+      </c>
+      <c r="N5" t="n">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N4"/>
+  <autoFilter ref="A1:N5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3752,71 +4230,71 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>45</v>
+        <v>67</v>
       </c>
       <c r="C2" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D2" t="n">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>48.9%</t>
+          <t>26.9%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>31.5%</t>
+          <t>30.6%</t>
         </is>
       </c>
       <c r="H2" t="n">
         <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="C3" t="n">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="D3" t="n">
-        <v>27</v>
+        <v>56</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>20.9%</t>
+          <t>47.5%</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>30.1%</t>
+          <t>26.9%</t>
         </is>
       </c>
       <c r="H3" t="n">
         <v>2</v>
       </c>
       <c r="I3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -3826,32 +4304,32 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="C4" t="n">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="D4" t="n">
-        <v>32</v>
+        <v>74</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>66.1%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>19.6%</t>
+          <t>25.6%</t>
         </is>
       </c>
       <c r="H4" t="n">
         <v>3</v>
       </c>
       <c r="I4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -3861,17 +4339,17 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C5" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D5" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>61.5%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -3879,42 +4357,42 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>9.1%</t>
+          <t>7.3%</t>
         </is>
       </c>
       <c r="H5" t="n">
         <v>4</v>
       </c>
       <c r="I5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Corner 3 Right</t>
+          <t>Corner 3 Left</t>
         </is>
       </c>
       <c r="B6" t="n">
+        <v>11</v>
+      </c>
+      <c r="C6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D6" t="n">
         <v>9</v>
       </c>
-      <c r="C6" t="n">
-        <v>2</v>
-      </c>
-      <c r="D6" t="n">
-        <v>6</v>
-      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>27.3%</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>6.3%</t>
+          <t>5.0%</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -3927,17 +4405,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Corner 3 Left</t>
+          <t>Corner 3 Right</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -3949,7 +4427,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>4.6%</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -3971,7 +4449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P12"/>
+  <dimension ref="A1:P13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -3982,7 +4460,7 @@
     <col width="19" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="17" customWidth="1" min="9" max="9"/>
+    <col width="19" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="16" customWidth="1" min="12" max="12"/>
@@ -4077,12 +4555,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>UDO_M._MORGAN</t>
+          <t>UDO_P._NIXON</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>M. Morgan</t>
+          <t>P. Nixon</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -4091,24 +4569,24 @@
         </is>
       </c>
       <c r="D2" t="n">
+        <v>15</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>26.7%</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
         <v>13</v>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>23.1%</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>6</v>
-      </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -4117,27 +4595,27 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>35.7%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="N2" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>26.7%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -4147,71 +4625,71 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>UDO_P._NIXON</t>
+          <t>UDO_M._MORGAN</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>P. Nixon</t>
+          <t>M. Morgan</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>15</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>26.7%</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>Paint Non-RA</t>
         </is>
       </c>
-      <c r="D3" t="n">
-        <v>11</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>36.4%</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
       <c r="G3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Mid-Range</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>80.0%</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>32.1%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>18.2%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="4">
@@ -4227,49 +4705,49 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>14</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t>Paint Non-RA</t>
         </is>
       </c>
-      <c r="D4" t="n">
-        <v>8</v>
-      </c>
-      <c r="E4" t="inlineStr">
+      <c r="G4" t="n">
+        <v>11</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>54.5%</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>2</v>
+      </c>
+      <c r="K4" t="inlineStr">
         <is>
           <t>50.0%</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
-        <v>7</v>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>42.9%</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Mid-Range</t>
-        </is>
-      </c>
-      <c r="J4" t="n">
-        <v>1</v>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
       <c r="L4" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>51.9%</t>
         </is>
       </c>
       <c r="N4" t="n">
@@ -4283,141 +4761,141 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>UDO_G._POWELL</t>
+          <t>UDO_J._TURNER</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>G. Powell</t>
+          <t>J. Turner</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>7</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>57.1%</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>6</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>83.3%</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
           <t>Above the Break 3</t>
         </is>
       </c>
-      <c r="D5" t="n">
-        <v>10</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>30.0%</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Mid-Range</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
-        <v>2</v>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
       <c r="J5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>26</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
           <t>50.0%</t>
         </is>
       </c>
-      <c r="L5" t="n">
-        <v>15</v>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>46.7%</t>
-        </is>
-      </c>
       <c r="N5" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>UDO_J._TURNER</t>
+          <t>UDO_G._POWELL</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>J. Turner</t>
+          <t>G. Powell</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>17</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>35.3%</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
           <t>Paint Non-RA</t>
         </is>
       </c>
-      <c r="D6" t="n">
-        <v>6</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>66.7%</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
       <c r="G6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Corner 3 Right</t>
+          <t>Mid-Range</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>48.0%</t>
         </is>
       </c>
       <c r="N6" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="7">
@@ -4437,24 +4915,24 @@
         </is>
       </c>
       <c r="D7" t="n">
+        <v>9</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>88.9%</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
         <v>5</v>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>80.0%</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="G7" t="n">
-        <v>3</v>
-      </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -4471,23 +4949,23 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="8">
@@ -4507,11 +4985,11 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>83.3%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -4520,16 +4998,16 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Mid-Range</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="J8" t="n">
@@ -4541,34 +5019,34 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>63.6%</t>
+          <t>58.8%</t>
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>UDO_T._DIAS</t>
+          <t>UDO_C._SA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>T. Dias</t>
+          <t>C. Sa</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -4577,127 +5055,127 @@
         </is>
       </c>
       <c r="D9" t="n">
+        <v>4</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>4</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
         <v>3</v>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>12</v>
+      </c>
+      <c r="M9" t="inlineStr">
         <is>
           <t>33.3%</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="G9" t="n">
-        <v>2</v>
-      </c>
-      <c r="H9" t="inlineStr">
+      <c r="N9" t="n">
+        <v>4</v>
+      </c>
+      <c r="O9" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="J9" t="n">
-        <v>1</v>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="L9" t="n">
-        <v>7</v>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>28.6%</t>
-        </is>
-      </c>
-      <c r="N9" t="n">
-        <v>2</v>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
       <c r="P9" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>UDO_C._SA</t>
+          <t>UDO_T._DIAS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>C. Sa</t>
+          <t>T. Dias</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>4</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>4</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
           <t>Restricted Area</t>
         </is>
       </c>
-      <c r="D10" t="n">
-        <v>3</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="G10" t="n">
+      <c r="J10" t="n">
         <v>2</v>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>Corner 3 Left</t>
-        </is>
-      </c>
-      <c r="J10" t="n">
-        <v>1</v>
-      </c>
       <c r="K10" t="inlineStr">
         <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>11</v>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>27.3%</t>
+        </is>
+      </c>
+      <c r="N10" t="n">
+        <v>4</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="L10" t="n">
-        <v>6</v>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
-      <c r="N10" t="n">
-        <v>1</v>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
       <c r="P10" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="11">
@@ -4763,12 +5241,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>UDO_R._CORREIA</t>
+          <t>UDO_M._FONSECA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>R. Correia</t>
+          <t>M. Fonseca</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -4777,37 +5255,97 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Corner 3 Left</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="N12" t="n">
+        <v>1</v>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>UDO_R._CORREIA</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>R. Correia</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="N12" t="n">
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="N13" t="n">
         <v>0</v>
       </c>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="n">
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="n">
         <v>2</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P12"/>
+  <autoFilter ref="A1:P13"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4818,7 +5356,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:K18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -4894,12 +5432,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>UDO_M._MORGAN</t>
+          <t>UDO_G._POWELL</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>M. Morgan</t>
+          <t>G. Powell</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -4908,88 +5446,88 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F2" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>35.3%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>46.4%</t>
+          <t>68.0%</t>
         </is>
       </c>
       <c r="J2" t="n">
         <v>1</v>
       </c>
       <c r="K2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>UDO_P._NIXON</t>
+          <t>UDO_M._MORGAN</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>P. Nixon</t>
+          <t>M. Morgan</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E3" t="n">
         <v>4</v>
       </c>
       <c r="F3" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>39.3%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="J3" t="n">
         <v>1</v>
       </c>
       <c r="K3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>UDO_G._POWELL</t>
+          <t>UDO_P._NIXON</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>G. Powell</t>
+          <t>P. Nixon</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -4998,74 +5536,74 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E4" t="n">
+        <v>4</v>
+      </c>
+      <c r="F4" t="n">
+        <v>12</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>26.7%</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>38.5%</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
         <v>3</v>
-      </c>
-      <c r="F4" t="n">
-        <v>9</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>30.0%</t>
-        </is>
-      </c>
-      <c r="H4" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>66.7%</t>
-        </is>
-      </c>
-      <c r="J4" t="n">
-        <v>1</v>
-      </c>
-      <c r="K4" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>UDO_P._NIXON</t>
+          <t>UDO_C._RODGER</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>P. Nixon</t>
+          <t>C. Rodger</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E5" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F5" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>35.7%</t>
+          <t>51.9%</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K5" t="n">
         <v>2</v>
@@ -5074,12 +5612,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>UDO_C._RODGER</t>
+          <t>UDO_P._NIXON</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>C. Rodger</t>
+          <t>P. Nixon</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -5088,32 +5626,32 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F6" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -5129,74 +5667,74 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E7" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F7" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>40.7%</t>
         </is>
       </c>
       <c r="J7" t="n">
         <v>2</v>
       </c>
       <c r="K7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>UDO_J._TURNER</t>
+          <t>UDO_J._ARAMBURU</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>J. Turner</t>
+          <t>J. Aramburu</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E8" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F8" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>88.9%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="J8" t="n">
@@ -5223,13 +5761,13 @@
         </is>
       </c>
       <c r="D9" t="n">
+        <v>9</v>
+      </c>
+      <c r="E9" t="n">
+        <v>3</v>
+      </c>
+      <c r="F9" t="n">
         <v>6</v>
-      </c>
-      <c r="E9" t="n">
-        <v>2</v>
-      </c>
-      <c r="F9" t="n">
-        <v>4</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -5241,34 +5779,34 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>21.4%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="J9" t="n">
         <v>2</v>
       </c>
       <c r="K9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>UDO_J._ARAMBURU</t>
+          <t>UDO_J._TURNER</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>J. Aramburu</t>
+          <t>J. Turner</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E10" t="n">
         <v>4</v>
@@ -5278,71 +5816,386 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>26.9%</t>
         </is>
       </c>
       <c r="J10" t="n">
         <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>UDO_J._TURNER</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>J. Turner</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>6</v>
+      </c>
+      <c r="E11" t="n">
+        <v>5</v>
+      </c>
+      <c r="F11" t="n">
+        <v>10</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>83.3%</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>23.1%</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>2</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>UDO_S._VICTO</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>S. Victo</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>Paint Non-RA</t>
         </is>
       </c>
-      <c r="D11" t="n">
+      <c r="D12" t="n">
+        <v>6</v>
+      </c>
+      <c r="E12" t="n">
         <v>5</v>
       </c>
-      <c r="E11" t="n">
+      <c r="F12" t="n">
+        <v>10</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>83.3%</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>35.3%</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>UDO_S._VICTO</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>S. Victo</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>6</v>
+      </c>
+      <c r="E13" t="n">
+        <v>3</v>
+      </c>
+      <c r="F13" t="n">
+        <v>6</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>35.3%</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>UDO_J._TURNER</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>J. Turner</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>6</v>
+      </c>
+      <c r="E14" t="n">
+        <v>2</v>
+      </c>
+      <c r="F14" t="n">
+        <v>6</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>1</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>23.1%</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>2</v>
+      </c>
+      <c r="K14" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>UDO_M._MORGAN</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>M. Morgan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>5</v>
+      </c>
+      <c r="E15" t="n">
         <v>4</v>
       </c>
-      <c r="F11" t="n">
+      <c r="F15" t="n">
         <v>8</v>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>80.0%</t>
         </is>
       </c>
-      <c r="H11" t="n">
+      <c r="H15" t="n">
         <v>1.6</v>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>45.5%</t>
-        </is>
-      </c>
-      <c r="J11" t="n">
-        <v>1</v>
-      </c>
-      <c r="K11" t="n">
-        <v>1</v>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>13.9%</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>3</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>UDO_P._NIXON</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>P. Nixon</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>5</v>
+      </c>
+      <c r="E16" t="n">
+        <v>2</v>
+      </c>
+      <c r="F16" t="n">
+        <v>4</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>12.8%</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>3</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>UDO_J._ARAMBURU</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>J. Aramburu</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>5</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F17" t="n">
+        <v>3</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>27.8%</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>2</v>
+      </c>
+      <c r="K17" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>UDO_J._TURNER</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>J. Turner</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Corner 3 Right</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>5</v>
+      </c>
+      <c r="E18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F18" t="n">
+        <v>3</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>19.2%</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>4</v>
+      </c>
+      <c r="K18" t="n">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K11"/>
+  <autoFilter ref="A1:K18"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>